--- a/协作/05-总览.xlsx
+++ b/协作/05-总览.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -622,6 +622,53 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>切片-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>协议 v3.5 全角色全开、零配置并补齐 37+3 交付物</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>APPROVE（16）</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PASS（18）</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>已合并（直接落库）</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>已发布（规范包 v3.5）</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>通过（发布-0001）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -633,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -817,9 +864,162 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>G0 完整性</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>证据-0008,证据-0009</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>G1 权限与篡改</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>证据-0010</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>G2 契约冻结</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>证据-0010</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>G3 溯源覆盖</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>证据-0009</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>G4 代码评审</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>G5 专项审查</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>证据-0009</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>G6 验收</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>证据-0011</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>G7 集成</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>证据-0010</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>G8 发布验收</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>证据-0010,证据-0011</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未触发,进行中,通过,阻断"</formula1>
     </dataValidation>
   </dataValidations>
@@ -905,7 +1105,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"范围,验收,风险,资源"</formula1>
     </dataValidation>
   </dataValidations>

--- a/协作/05-总览.xlsx
+++ b/协作/05-总览.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -666,6 +666,53 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>通过（发布-0001）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>切片-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>协议与模板外置到 TEAMODEL 仓库，DCG 只按标签引用</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>APPROVE（16）</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PASS（18）</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>已合并（直接落库）</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>不适用（非发布切片）</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>通过（验收-0008）</t>
         </is>
       </c>
     </row>

--- a/协作/05-总览.xlsx
+++ b/协作/05-总览.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -713,6 +713,53 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>通过（验收-0008）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>切片-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>README 去掉 v2 版本叙事，把「定位」改为适配场景</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>APPROVE（16）</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PASS（18）</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>已合并（直接落库）</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>不适用（非发布切片）</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>通过（验收-0009）</t>
         </is>
       </c>
     </row>

--- a/协作/05-总览.xlsx
+++ b/协作/05-总览.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -760,6 +760,53 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>通过（验收-0009）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>切片-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>README 写明：JSONata 是结构描述语言、编译成固化 Python 提效、主场景为任意数据结构转换</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>APPROVE（16）</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PASS（18）</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>已合并（直接落库）</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>不适用（非发布切片）</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>通过（验收-0010）</t>
         </is>
       </c>
     </row>

--- a/协作/05-总览.xlsx
+++ b/协作/05-总览.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -807,6 +807,53 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>通过（验收-0010）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>切片-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>README 删除基线/修订锚点段与 §0.1–§0.3 三个子节，§0 只保留主场景</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>APPROVE（16）</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PASS（18）</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>已合并（直接落库）</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>不适用（非发布切片）</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>通过（验收-0011）</t>
         </is>
       </c>
     </row>
